--- a/Codelist Excel Files and Conversion Templates to XML/samplerInsertionMethod.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/samplerInsertionMethod.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes classifying how a sampler is advanced into the ground, planned or realized - pushed, driven, rotated, vibrated. Used for the value of diggs:TargetSampleType/samplerInsertionMethod (planned) and diggs:AbstractSamplingActivityType/samplerInsertionMethod (as-built, currently realized only by diggs:SamplingActivity) so design and as-built share one vocabulary for the same concept.</t>
+          <t>Codes classifying how a sampler is advanced into the ground, planned or realized - pushed, driven, rotated, vibrated. Used for the value of diggs:DesignSampleType/samplerInsertionMethod (planned) and diggs:AbstractSamplingActivityType/samplerInsertionMethod (as-built, currently realized only by diggs:SamplingActivity) so design and as-built share one vocabulary for the same concept.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>//diggs:TargetSample/diggs:samplerInsertionMethod</t>
+          <t>//diggs:DesignSample/diggs:samplerInsertionMethod</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//diggs:TargetSample/diggs:samplerInsertionMethod</t>
+          <t>//diggs:DesignSample/diggs:samplerInsertionMethod</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>//diggs:TargetSample/diggs:samplerInsertionMethod</t>
+          <t>//diggs:DesignSample/diggs:samplerInsertionMethod</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>//diggs:TargetSample/diggs:samplerInsertionMethod</t>
+          <t>//diggs:DesignSample/diggs:samplerInsertionMethod</t>
         </is>
       </c>
     </row>
